--- a/output/orders.xlsx
+++ b/output/orders.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="550" windowWidth="15040" windowHeight="6740"/>
+    <workbookView xWindow="190" yWindow="520" windowWidth="10240" windowHeight="3740"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
